--- a/src/main/kotlin/com/kcvn/spm/assets/template/TemplateExportCompleteRateError.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/TemplateExportCompleteRateError.xlsx
@@ -35,9 +35,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -118,7 +119,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -127,11 +128,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -153,7 +158,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.07"/>
@@ -161,13 +166,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/TemplateExportCompleteRateError.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/TemplateExportCompleteRateError.xlsx
@@ -40,7 +40,7 @@
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -63,17 +63,31 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -119,24 +133,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -158,21 +180,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="17.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="22.79"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
